--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -675,40 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133827887</v>
+        <v>133827913</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,35 +782,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133827913</v>
+        <v>133827887</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1238,7 +1238,7 @@
         <v>133826516</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -675,35 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133827913</v>
+        <v>133827887</v>
       </c>
       <c r="B2" t="n">
-        <v>8455</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,40 +787,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133827887</v>
+        <v>133827913</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133826844</v>
+        <v>133826516</v>
       </c>
       <c r="B6" t="n">
-        <v>8455</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489687</v>
+        <v>489651</v>
       </c>
       <c r="R6" t="n">
-        <v>6671333</v>
+        <v>6671439</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133826516</v>
+        <v>133826844</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>8455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489651</v>
+        <v>489687</v>
       </c>
       <c r="R7" t="n">
-        <v>6671439</v>
+        <v>6671333</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -675,40 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133827887</v>
+        <v>133827913</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,35 +782,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133827913</v>
+        <v>133827887</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
         <v>133828445</v>
       </c>
       <c r="B4" t="n">
-        <v>57136</v>
+        <v>57143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>133827417</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>133826516</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>133826844</v>
       </c>
       <c r="B7" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133826516</v>
+        <v>133826844</v>
       </c>
       <c r="B6" t="n">
-        <v>79348</v>
+        <v>8460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489651</v>
+        <v>489687</v>
       </c>
       <c r="R6" t="n">
-        <v>6671439</v>
+        <v>6671333</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133826844</v>
+        <v>133826516</v>
       </c>
       <c r="B7" t="n">
-        <v>8460</v>
+        <v>79348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489687</v>
+        <v>489651</v>
       </c>
       <c r="R7" t="n">
-        <v>6671333</v>
+        <v>6671439</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>133827887</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>133828445</v>
       </c>
       <c r="B4" t="n">
-        <v>57143</v>
+        <v>57153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>133827417</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>133826516</v>
       </c>
       <c r="B7" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -675,35 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133827913</v>
+        <v>133827887</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,40 +787,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133827887</v>
+        <v>133827913</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -675,40 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133827887</v>
+        <v>133827913</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,35 +782,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133827913</v>
+        <v>133827887</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133826844</v>
+        <v>133826516</v>
       </c>
       <c r="B6" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489687</v>
+        <v>489651</v>
       </c>
       <c r="R6" t="n">
-        <v>6671333</v>
+        <v>6671439</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133826516</v>
+        <v>133826844</v>
       </c>
       <c r="B7" t="n">
-        <v>79358</v>
+        <v>8460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489651</v>
+        <v>489687</v>
       </c>
       <c r="R7" t="n">
-        <v>6671439</v>
+        <v>6671333</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -675,35 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133827913</v>
+        <v>133827887</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,40 +787,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133827887</v>
+        <v>133827913</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133826844</v>
+        <v>133826516</v>
       </c>
       <c r="B6" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489687</v>
+        <v>489651</v>
       </c>
       <c r="R6" t="n">
-        <v>6671333</v>
+        <v>6671439</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133826516</v>
+        <v>133826844</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489651</v>
+        <v>489687</v>
       </c>
       <c r="R7" t="n">
-        <v>6671439</v>
+        <v>6671333</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -675,40 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133827887</v>
+        <v>133827913</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>8460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,35 +782,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133827913</v>
+        <v>133827887</v>
       </c>
       <c r="B3" t="n">
-        <v>8460</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1128,32 +1128,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133826516</v>
+        <v>133826844</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489651</v>
+        <v>489687</v>
       </c>
       <c r="R6" t="n">
-        <v>6671439</v>
+        <v>6671333</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133826844</v>
+        <v>133826516</v>
       </c>
       <c r="B7" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489687</v>
+        <v>489651</v>
       </c>
       <c r="R7" t="n">
-        <v>6671333</v>
+        <v>6671439</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 23711-2026 artfynd.xlsx
+++ b/artfynd/A 23711-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133827913</v>
+        <v>133846943</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489694</v>
+        <v>489681</v>
       </c>
       <c r="R2" t="n">
-        <v>6671451</v>
+        <v>6671302</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -743,19 +743,9 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133827887</v>
+        <v>133826516</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489694</v>
+        <v>489651</v>
       </c>
       <c r="R3" t="n">
-        <v>6671451</v>
+        <v>6671439</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,27 +879,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133828445</v>
+        <v>133827417</v>
       </c>
       <c r="B4" t="n">
-        <v>57153</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -923,14 +908,9 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -939,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489674</v>
+        <v>489708</v>
       </c>
       <c r="R4" t="n">
-        <v>6671389</v>
+        <v>6671388</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:35</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Svarar på min lockpipa</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,14 +991,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133827417</v>
+        <v>133827887</v>
       </c>
       <c r="B5" t="n">
         <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1056,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489708</v>
+        <v>489694</v>
       </c>
       <c r="R5" t="n">
-        <v>6671388</v>
+        <v>6671451</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133826844</v>
+        <v>133828445</v>
       </c>
       <c r="B6" t="n">
-        <v>8460</v>
+        <v>57153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1114,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarntäppan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>489687</v>
+        <v>489674</v>
       </c>
       <c r="R6" t="n">
-        <v>6671333</v>
+        <v>6671389</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1193,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Svarar på min lockpipa</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,32 +1225,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133826516</v>
+        <v>133826844</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489651</v>
+        <v>489687</v>
       </c>
       <c r="R7" t="n">
-        <v>6671439</v>
+        <v>6671333</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1305,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,6 +1329,113 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133827913</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvarntäppan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>489694</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6671451</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
